--- a/data/csv_files/demo_data/ohio/demo_ohio.xlsx
+++ b/data/csv_files/demo_data/ohio/demo_ohio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/G_PSYPLAFOR_methlab$/EEGManyLabs/data/csv_files/demo_data/dartmouth/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/G_PSYPLAFOR_methlab$/EEGManyLabs/data/csv_files/demo_data/ohio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C05BE-10C3-B344-BE4E-97564BDA2B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19B1AEA-8BDC-144F-8659-AE1CE0AA4694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1400" windowWidth="28240" windowHeight="17100" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
+    <workbookView xWindow="1160" yWindow="860" windowWidth="28240" windowHeight="17100" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -60,13 +60,25 @@
   </si>
   <si>
     <t>Handedness</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Normal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -74,13 +86,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -95,8 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -431,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C03222-1F27-AC4C-9C40-659F3B91E4D1}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="7" width="15.5" customWidth="1"/>
@@ -464,6 +498,384 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2">
+        <v>28</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2">
+        <v>25</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>19</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/csv_files/demo_data/ohio/demo_ohio.xlsx
+++ b/data/csv_files/demo_data/ohio/demo_ohio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/G_PSYPLAFOR_methlab$/EEGManyLabs/data/csv_files/demo_data/ohio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19B1AEA-8BDC-144F-8659-AE1CE0AA4694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC108250-B003-954B-817C-775C9FE34380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="860" windowWidth="28240" windowHeight="17100" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
+    <workbookView xWindow="1160" yWindow="800" windowWidth="28240" windowHeight="17100" xr2:uid="{813DB4F9-C551-4443-B74D-BE5D3A3DD756}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -68,17 +68,17 @@
     <t>M</t>
   </si>
   <si>
-    <t>f</t>
+    <t>Normal</t>
   </si>
   <si>
-    <t>Normal</t>
+    <t>NA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -98,6 +98,13 @@
       <color theme="1"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,16 +130,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{0DE2B463-64DB-1843-9B2E-CAAD99FF9416}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -465,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C03222-1F27-AC4C-9C40-659F3B91E4D1}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="7" width="15.5" customWidth="1"/>
@@ -509,6 +521,18 @@
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -523,6 +547,18 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -537,6 +573,18 @@
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -551,6 +599,18 @@
         <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -565,6 +625,18 @@
         <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -579,6 +651,18 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -593,6 +677,18 @@
         <v>8</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -607,6 +703,18 @@
         <v>8</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -621,6 +729,18 @@
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -635,6 +755,18 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -649,6 +781,18 @@
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -657,224 +801,367 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>21</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>28</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>18</v>
-      </c>
-      <c r="B21" s="1">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2">
-        <v>28</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>22</v>
-      </c>
-      <c r="B25" s="2">
+      <c r="D25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>23</v>
-      </c>
       <c r="B26" s="1">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1">
-        <v>23</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1">
-        <v>26</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E27" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
